--- a/tasks/finalpool/terminal-canvas-pdf-excel-notion-gcal/groundtruth_workspace/Accreditation_Self_Study.xlsx
+++ b/tasks/finalpool/terminal-canvas-pdf-excel-notion-gcal/groundtruth_workspace/Accreditation_Self_Study.xlsx
@@ -946,7 +946,7 @@
         <v>0.65</v>
       </c>
       <c r="C3" t="n">
-        <v>0.59</v>
+        <v>0.64</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -964,11 +964,11 @@
         <v>3.5</v>
       </c>
       <c r="C4" t="n">
-        <v>4.9</v>
+        <v>0.19</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Compliant</t>
+          <t>Non-Compliant</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1128,7 +1128,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Actual value 0.59 is below threshold 0.65</t>
+          <t>Actual value 0.64 is below threshold 0.65</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1161,6 +1161,28 @@
       <c r="D4" t="inlineStr">
         <is>
           <t>Within 6 months</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>C3: Student Retention</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Actual value 0.19 is far below threshold 3.5</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Implement retention improvement initiatives (mentoring and early-alert programs)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Within 12 months</t>
         </is>
       </c>
     </row>
